--- a/stck sheet.xlsx
+++ b/stck sheet.xlsx
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">

--- a/stck sheet.xlsx
+++ b/stck sheet.xlsx
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124" ht="21" customHeight="1">
